--- a/production_lines details.xlsx
+++ b/production_lines details.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Saiyd\Desktop\AI_Project\birma_production\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FD7AF09-86CC-470A-AEC8-601500FB563F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B8D9EE0-E21D-4443-A798-FD784EEC1610}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="18">
   <si>
     <t xml:space="preserve">خط انتاج 1 </t>
   </si>
@@ -61,6 +61,24 @@
   </si>
   <si>
     <t>331 مل شرنك</t>
+  </si>
+  <si>
+    <t>عدد البريفورم</t>
+  </si>
+  <si>
+    <t>معدلات الخصم</t>
+  </si>
+  <si>
+    <t>عدد الغطاء</t>
+  </si>
+  <si>
+    <t>عدد الليبل</t>
+  </si>
+  <si>
+    <t>عدد الكرتون الخام/ الشرنك</t>
+  </si>
+  <si>
+    <t>330 مل شرنك</t>
   </si>
 </sst>
 </file>
@@ -102,8 +120,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -387,17 +408,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:F8"/>
+  <dimension ref="A2:H18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -417,8 +440,8 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B3" t="s">
@@ -437,8 +460,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1"/>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="2"/>
       <c r="B4" t="s">
         <v>4</v>
       </c>
@@ -455,7 +478,7 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>1</v>
       </c>
@@ -472,8 +495,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B7" t="s">
@@ -492,8 +515,8 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1"/>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="2"/>
       <c r="B8" t="s">
         <v>4</v>
       </c>
@@ -510,10 +533,146 @@
         <v>40000</v>
       </c>
     </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="1"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="1"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12" t="s">
+        <v>5</v>
+      </c>
+      <c r="E12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" t="s">
+        <v>17</v>
+      </c>
+      <c r="G12" t="s">
+        <v>6</v>
+      </c>
+      <c r="H12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="2"/>
+      <c r="B13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13">
+        <v>48</v>
+      </c>
+      <c r="D13">
+        <v>20</v>
+      </c>
+      <c r="E13">
+        <v>40</v>
+      </c>
+      <c r="F13">
+        <v>20</v>
+      </c>
+      <c r="G13">
+        <v>30</v>
+      </c>
+      <c r="H13">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="2"/>
+      <c r="B14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14">
+        <v>48</v>
+      </c>
+      <c r="D14">
+        <v>20</v>
+      </c>
+      <c r="E14">
+        <v>40</v>
+      </c>
+      <c r="F14">
+        <v>20</v>
+      </c>
+      <c r="G14">
+        <v>30</v>
+      </c>
+      <c r="H14">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15">
+        <v>48</v>
+      </c>
+      <c r="D15">
+        <v>20</v>
+      </c>
+      <c r="E15">
+        <v>40</v>
+      </c>
+      <c r="F15">
+        <v>20</v>
+      </c>
+      <c r="G15">
+        <v>30</v>
+      </c>
+      <c r="H15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2"/>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2"/>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="A7:A8"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="A17:A18"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
